--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_04_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_04_21_Cau.xlsx
@@ -727,7 +727,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>51.2</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
@@ -741,7 +745,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: ‘Tất cả k lần’ dùng p^k, không phải pass@k.</t>
+          <t>Xác suất pass^3 cho cả 3 run liên tiếp độc lập thành công với p=0,8: pass^3 = p^3 = 0,8^3 = 0,512 = 51,2%.</t>
         </is>
       </c>
     </row>
@@ -793,7 +797,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>99.2</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
@@ -807,7 +815,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng complement của việc cả ba lần đều fail.</t>
+          <t>Xác suất pass@3 (ít nhất một lần thành công trong 3 lần thử độc lập): pass@3 = 1 - (1 - p)^3 = 1 - (1 - 0,8)^3 = 1 - 0,2^3 = 1 - 0,008 = 0,992 = 99,2%.</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1355,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>1216</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
@@ -1361,7 +1373,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính update từ chênh lệch observed và expected.</t>
+          <t>Công thức Elo: R'_A = R_A + K * (observed - expected) = 1200 + 32 * (1 - 0,5) = 1200 + 16 = 1216.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_04_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_04_21_Cau.xlsx
@@ -624,10 +624,28 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một payload có thể đồng thời fail structure và grounding.
-Phân tích theo nguyên lý thiết kế: Một payload có thể đồng thời fail structure và grounding.</t>
+- 1.0đ: Gán đúng nhãn lỗi Schema Type Mismatch cho trường `date`.
+- 1.0đ: Gán đúng nhãn lỗi nghiêm trọng Argument Hallucination / Unfaithful State Fabrication cho trường `passport number`.
+- 1.0đ: Thiết kế bộ Evaluator Tầng 1 kiểm tra kiểu dữ liệu nghiêm ngặt bằng Pydantic/Validator.
+- 1.0đ: Thiết kế bộ Evaluator Tầng 2 kiểm tra nguồn gốc dữ liệu (State Grounding / Provenance) chặn đứng hành vi tự bịa tham số.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại và Gán Nhãn Lỗi (Error Taxonomy Assignment):
+- Mặc dù Agent đã chọn đúng công cụ `book_flight` và payload vượt qua kiểm tra cú pháp JSON cơ bản, nhưng có 2 lỗi nghiêm trọng:
+- **Lỗi 1: Type/Format Validation Error (Lỗi Định dạng Kiểu Dữ liệu)**:
+  + *Gán lỗi*: `SCHEMA_TYPE_MISMATCH`.
+  + *Bản chất*: Trường `date` truyền sai kiểu dữ liệu (ví dụ: truyền chuỗi văn bản tự do 'thứ hai tuần tới' hoặc số nguyên timestamp thay vì định dạng chuẩn ISO-8601 `YYYY-MM-DD`). Đây là lỗi cú pháp ngữ nghĩa ở tầng giao tiếp API.
+- **Lỗi 2: Argument Hallucination / Unfaithful State Fabrication (Lỗi Ảo giác Tham số)**:
+  + *Gán lỗi*: `CRITICAL_SECURITY_HALLUCINATION_UNGROUNDED_ARG`.
+  + *Bản chất*: Agent tự ý bịa đặt số hộ chiếu (passport number) hoàn toàn không có trong lịch sử trò chuyện (user prompt) lẫn trạng thái phiên làm việc (session state). Đây là lỗi an toàn cực kỳ nguy hiểm, có thể dẫn đến việc đặt vé sai danh tính hoặc vi phạm pháp luật hàng không.
+2. Thiết kế Bộ Đánh giá Khắc phục (Remediation Evaluator Pipeline):
+- **Tầng 1: Pre-flight Strict Schema &amp; Type Validator**:
+  Sử dụng Pydantic v2 / Zod validator kiểm tra kiểu dữ liệu `date` bằng regex nghiêm ngặt trước khi gửi payload đi.   Nếu sai type, chặn lại ngay lập tức và ném lỗi phản hồi chuẩn cho Agent: `Date must follow ISO-8601 format`.
+- **Tầng 2: Argument Provenance &amp; State Grounding Evaluator**:
+  Chạy bộ đối soát nguồn gốc tham số: Mọi tham số nhạy cảm (như passport, CCCD, số thẻ tín dụng) phải có xuất xứ chứng minh được trong Context/User State (`is_grounded_in_state == True`).   Nếu tham số không thể trích xuất từ dữ liệu người dùng cung cấp, Evaluator phát cờ chặn khẩn cấp `UNAUTHORIZED_FABRICATED_ARGUMENT` và yêu cầu Agent hỏi trực tiếp người dùng thay vì tự bịa.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thẩm định Tham số Lời gọi Công cụ (Tool Payload Evaluation): Một lời gọi công cụ hợp lệ không chỉ cần vượt qua cú pháp (Schema Validation) mà phải bảo đảm tính trung thực của tham số (Argument Faithfulness). Hiện tượng Agent tự 'sáng tác' số hộ chiếu hoặc số tài khoản khi người dùng chưa cung cấp là rủi ro rò rỉ và giả mạo dữ liệu hàng đầu. Bộ thẩm định phải kết hợp cả Type Validator (cho trường date) và State Grounding Checker (cho trường passport) để bảo đảm an toàn giao dịch.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Pydantic Documentation &amp; OWASP Top 10 for LLM: LLM08 Excessive Agency &amp; Tool Verification Frameworks</t>
         </is>
       </c>
     </row>
@@ -706,10 +724,31 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Ba failure mode input cần behavior oracle riêng.
-Phân tích theo nguyên lý thiết kế: Ba failure mode input cần behavior oracle riêng.</t>
+- 1.0đ: Thiết kế Oracle chuẩn cho Case 1 (Missing account): cấm gọi tool giao dịch, bắt buộc hỏi xin số tài khoản.
+- 1.0đ: Thiết kế Oracle chuẩn cho Case 2 (Ambiguous accounts): cấm tự đoán, bắt buộc liệt kê cả hai lựa chọn để người dùng xác nhận.
+- 1.0đ: Thiết kế Oracle chuẩn cho Case 3 (Invalid format): cấm gửi request rác, bắt buộc chỉ ra lỗi định dạng và yêu cầu nhập lại.
+- 1.0đ: Thể hiện đúng cấu trúc Oracle có thể kiểm chứng tự động (kết hợp cả Forbidden Negative và Required Positive conditions).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Trọng tài Quan sát được (Observable Oracles) cho Ba Trường hợp Thiếu / Mơ hồ Thông tin:
+1. **Case 1: Khuyết thiếu Số tài khoản Hoàn toàn (Missing Account Case)**:
+- *Ngữ cảnh*: Người dùng yêu cầu 'Chuyển cho tôi 5 triệu' nhưng không hề cung cấp số tài khoản nguồn hay đích.
+- **Observable Oracle Contract**:
+  + **Điều kiện CẤM (Forbidden Negative Condition)**: Agent **TUYỆT ĐỐI KHÔNG ĐƯỢC GỌI** bất kỳ công cụ giao dịch nào (`len(tool_calls) == 0`).
+  + **Điều kiện BẮT BUỘC (Required Positive Condition)**: Câu trả lời văn bản của Agent phải chứa hành vi yêu cầu cung cấp thông tin: `re.search(r'(cung cấp|cho biết|nhập).*(số tài khoản|tài khoản)', response, re.I) is not None`.
+2. **Case 2: Có Hai Tài khoản nhưng Bị Mơ hồ (Ambiguous Accounts Case)**:
+- *Ngữ cảnh*: Người dùng có cả 'Tài khoản Tiết kiệm' và 'Tài khoản Thanh toán', người dùng chỉ bảo 'Chuyển tiền đi'.
+- **Observable Oracle Contract**:
+  + **Điều kiện CẤM**: Không được tự ý đoán mò chọn một trong hai tài khoản để thực hiện giao dịch ngầm.
+  + **Điều kiện BẮT BUỘC**: Agent phải liệt kê danh sách cả 2 tài khoản và yêu cầu người dùng chỉ định rõ ràng:     `assert 'Tiết kiệm' in response and 'Thanh toán' in response and 'chọn' in response.lower()`.
+3. **Case 3: Số tài khoản Sai Định dạng Cú pháp (Invalid Account Format Case)**:
+- *Ngữ cảnh*: Người dùng cung cấp số tài khoản chứa chữ cái hoặc chỉ có 4 chữ số trong khi chuẩn ngân hàng là 10 số.
+- **Observable Oracle Contract**:
+  + **Điều kiện CẤM**: Không gọi API ngân hàng với số tài khoản rác (ngăn chặn lãng phí tải mạng và lỗi 400).
+  + **Điều kiện BẮT BUỘC**: Agent phát hiện ngay lỗi định dạng ở tầng giao tiếp và giải thích cụ thể:     `assert 'không hợp lệ' in response.lower() and ('10 chữ số' in response or 'chỉ bao gồm số' in response)`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Đánh giá Năng lực Tự làm rõ Thông tin (Clarification &amp; Ambiguity Handling Evaluation): Một con Agent an toàn không phải là con Agent luôn luôn cố gắng gọi công cụ bằng mọi giá. Khi gặp thông tin thiếu, mơ hồ hoặc sai định dạng, hành vi đúng đắn duy nhất là **DỪNG LẠI VÀ HỎI LÀM RÕ** (Clarification Dialogue). Các Oracle quan sát được phải kiểm tra đồng thời cả hai vế: vế phủ định (không gọi tool bừa bãi) và vế khẳng định (đặt câu hỏi làm rõ chính xác).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+CoQA: A Conversational Question Answering Challenge (Siva Reddy et al., TACL 2019) &amp; Task-Oriented Dialogue Clarification Benchmarks</t>
         </is>
       </c>
     </row>
@@ -776,10 +815,31 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phân biệt retry success với reliability mọi lần.
-Phân tích theo nguyên lý thiết kế: Phân biệt retry success với reliability mọi lần.</t>
+- 1.0đ: Thiết lập đúng công thức xác suất phần bù cho pass@3: $1 - (1 - p)^3$.
+- 1.0đ: Tính toán số học chính xác: $1 - 0.3^3 = 1 - 0.027 = 0.973$ (hoặc 97.3%).
+- 1.0đ: Phân tích sâu sắc giới hạn vi phạm giả định độc lập khi gặp lỗi có tính hệ thống.
+- 1.0đ: Chỉ ra hệ quả tiêu cực về chi phí token tăng gấp 3 và độ trễ đuôi (tail latency) kéo dài.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Chỉ số pass@3 cho Agent Ngẫu nhiên (Stochastic Agent Reliability):
+- Dữ liệu bài toán:
+  + Xác suất thành công của một lần chạy đơn lẻ: $p = 0.70$ ($70\%$).
+  + Số lần chạy tối đa cho phép: $k = 3$ lần.
+  + Giả định: Các lần chạy hoàn toàn độc lập về mặt xác suất (Independent and Identically Distributed - i.i.d.).
+  + Điều kiện thành công của sản phẩm: Chỉ cần có **ít nhất một lần thành công** trong tối đa 3 lần chạy.
+- **Tính xác suất một lần chạy bị thất bại**: $q = 1 - p = 1 - 0.70 = 0.30$ ($30\%$).
+- **Tính xác suất cả 3 lần chạy đều thất bại**:
+  $$P(\text{thất bại cả 3 lần}) = q^3 = (0.30)^3 = 0.027 \quad (2.7\%$$
+- **Tính chỉ số pass@3 (Xác suất có ít nhất một lần thành công)**:
+  $$\text{pass@3} = 1 - P(\text{thất bại cả 3 lần}) = 1 - 0.027 = \mathbf{0.973} \quad (97.3\%$$
+- Nhận xét: Nhờ cơ chế retry 3 lần, tỷ lệ thành công tổng thể của tính năng được nâng từ 70% lên tới 97.3%.
+2. Giới hạn Cốt tử của Chỉ số pass@3 trong Vận hành Sản xuất (Operational Limitations):
+- **Vi phạm Giả định Độc lập trong Lỗi Có Hệ thống (Systematic Failure Correlation)**: Nếu Agent thất bại ở lần 1 do câu hỏi nằm ngoài phạm vi tri thức (out-of-distribution) hoặc do prompt chứa lỗi logic cơ bản, các lần chạy 2 và 3 có xác suất thất bại gần như 100% cùng chung một lỗi, khiến con số lý thuyết 97.3% bị sụp đổ hoàn toàn.
+- **Bùng nổ Chi phí và Độ trễ Tệ nhất (Worst-case Cost &amp; Latency Explosion)**: Để đạt được pass@3, hệ thống trong trường hợp xấu nhất phải tiêu tốn gấp 3 lần chi phí token và bắt người dùng chờ đợi gấp 3 lần thời gian (P99 latency tăng 300%).
+- **Tính Bất nhất của Trải nghiệm Người dùng (Stochastic Inconsistency)**: Cùng một câu hỏi, lần này chạy được, lần sau chạy lỗi, làm giảm độ tin cậy của sản phẩm trong mắt khách hàng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khái niệm pass@k (HumanEval Benchmark - Chen et al., 2021): Chỉ số pass@k đo lường khả năng giải quyết vấn đề khi cho phép mô hình thử $k$ lần. Về mặt toán học xác suất, pass@k tăng rất nhanh theo công thức phần bù $1 - (1-p)^k$. Tuy nhiên, dựa dẫm vào pass@k trên production là con dao hai lưỡi: nó che giấu sự bất ổn định cố hữu của mô hình, làm tăng gấp ba chi phí vận hành và hoàn toàn vô tác dụng trước các lỗi có tính hệ thống (systemic prompt flaws).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Mark Chen et al.: Evaluating Large Language Models Trained on Code (HumanEval pass@k Formulation, OpenAI 2021)</t>
         </is>
       </c>
     </row>
@@ -894,10 +954,28 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Session-level constraint phải sống qua context trung gian.
-Phân tích theo nguyên lý thiết kế: Session-level constraint phải sống qua context trung gian.</t>
+- 1.0đ: Phân tích đúng cơ chế gây lỗi suy thoái ràng buộc do pha loãng chú ý ngữ cảnh đường dài (attention dilution).
+- 1.0đ: Thiết kế máy trạng thái lưu giữ ràng buộc tích lũy xuyên suốt các lượt trò chuyện (Cumulative Constraint Registry).
+- 1.0đ: Xây dựng cơ chế kiểm tra đối soát tự động payload công cụ ở lượt sau với ràng buộc ở lượt trước.
+- 1.0đ: Định nghĩa các chỉ số đo lường định lượng sự suy thoái theo khoảng cách số lượt trò chuyện.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Hệ thống Đánh giá Phiên Hội thoại Đa lượt để Phát hiện Suy thoái Ràng buộc (Multiturn Constraint Decay Eval):
+1. **Bản chất của Hiện tượng Suy thoái Ràng buộc (Constraint Decay / Lost-in-the-Middle)**:
+Người dùng đưa ra ràng buộc ngân sách cứng ở Lượt 1 ('không mua nếu giá &gt; 2 triệu'). Qua các lượt 2, 3, 4, 5 với nhiều chủ đề thảo luận trung gian, thông tin ràng buộc bị đẩy xa khỏi cửa sổ ngữ cảnh tập trung (Attention Dilution). Đến Lượt 6, Agent tự động kích hoạt công cụ mua hàng với giá 2.4 triệu VNĐ. Đây là sự đứt gãy năng lực ghi nhớ ràng buộc đường dài.
+2. **Thiết kế Khung Đánh giá Phiên Hội thoại (Session Evaluation Architecture)**:
+- **Bộ Đăng ký Ràng buộc Tích lũy (Cumulative Constraint Registry State Machine)**:
+  Xây dựng một evaluator theo dõi toàn bộ phiên chat: Mỗi khi người dùng phát ngôn, một mô hình trích xuất luật tự động ghi nhận các ràng buộc tích lũy:   `active_constraints = [{'id': 'c1', 'turn': 1, 'type': 'max_price', 'limit': 2000000}]`.
+- **Trọng tài Thẩm định Payload Từng Bước (Step-by-Step Payload Assertion Oracle)**:
+  Tại mỗi lượt Agent kích hoạt công cụ (Turn 6: `tool_name = 'purchase'`, `payload = {'price': 2400000}`):
+  Evaluator tự động đem payload đối soát với **toàn bộ danh sách active_constraints từ quá khứ**:
+  `assert payload['price'] &lt;= 2000000, f'Vi phạm ràng buộc c1 từ Turn 1: 2.4tr &gt; 2.0tr'`.
+3. **Chỉ số Đo lường Suy thoái Ngữ cảnh (Decay Metrics)**:
+- `constraint_survival_turn_distance`: Đo lường khoảng cách số lượt trung gian mà Agent duy trì được ràng buộc trước khi bị vi phạm.
+- `multiturn_constraint_violation_rate`: Tỷ lệ các phiên hội thoại vi phạm luật cũ khi độ dài cuộc trò chuyện vượt quá 5 lượt.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Đánh giá Đa lượt trong Hội thoại AI (Multi-turn Constraint Tracking): Kiểm thử đơn lượt (Single-turn eval) hoàn toàn bất lực trong việc phát hiện lỗi này vì trong một lượt đơn lẻ, prompt thường ngắn. Trong môi trường đa lượt (Multi-turn Agent), sự chú ý của mô hình suy giảm mạnh đối với các chỉ thị ở xa (Context Decay). Một khung đánh giá chuẩn mực phải duy trì một State Machine lưu giữ các ràng buộc bất biến xuyên suốt phiên làm việc và thực hiện assertion trên từng payload công cụ phát sinh.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Nelson F. Liu et al.: Lost in the Middle: How Language Models Use Long Contexts (TACL 2024) &amp; Multi-turn Benchmark Standards</t>
         </is>
       </c>
     </row>
@@ -1032,10 +1110,27 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: User exit và task resolution là hai biến riêng.
-Phân tích theo nguyên lý thiết kế: User exit và task resolution là hai biến riêng.</t>
+- 1.0đ: Phân loại chuẩn xác Phiên 1 là Thành công hoàn tất nhiệm vụ (Goal-Achieved Resolution).
+- 1.0đ: Phân loại chuẩn xác Phiên 2 là Rời bỏ do ức chế độ trễ/chờ đợi (Frustrated Latency Abandonment).
+- 1.0đ: Phân tích sâu sắc giới hạn suy diễn của tín hiệu hành vi ngầm định (đóng tab có thể do yếu tố ngoại cảnh).
+- 1.0đ: Nêu rõ nguyên tắc xác nhận kép dựa trên trạng thái môi trường thực tế trước khi đưa ra kết luận.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại Kết quả Hai Phiên Hội thoại (Session Outcome Taxonomy):
+- **Phiên 1 (User đóng chat sau khi nhận đúng kết quả và đạt target state)**:
+  + **Phân loại**: **Thành công Hoàn tất Nhiệm vụ / Rời đi Hài lòng (Goal-Achieved Resolution / Clean Exit)**.
+  + *Bản chất*: Mục tiêu của người dùng đã được giải quyết trọn vẹn. Trạng thái nghiệp vụ (target state) được môi trường xác nhận là hoàn thành. Việc người dùng đóng tab ngay sau đó là hành vi tự nhiên khi nhu cầu kết thúc, không phải lỗi.
+- **Phiên 2 (User rời đi khi công cụ đang trong trạng thái chờ xử lý pending)**:
+  + **Phân loại**: **Rời bỏ do Ức chế Độ trễ / Gián đoạn Trải nghiệm (Frustrated Latency Abandonment / Incomplete Drop-off)**.
+  + *Bản chất*: Công cụ thực thi quá chậm hoặc hệ thống bị treo không phản hồi kịp thời, khiến người dùng mất kiên nhẫn và bỏ dở tác vụ giữa chừng mà mục tiêu chưa đạt được.
+2. Giới hạn Suy diễn Hành vi (Inference Boundaries &amp; Latent Intent Limits):
+- **Cạm bẫy Suy đoán Tâm lý (Latent Intent Uncertainty)**: Hành vi đóng tab hoặc rời bỏ màn hình là tín hiệu gián tiếp (Implicit Signal), không phải thước đo chân lý tuyệt đối:
+  + Ở Phiên 1, người dùng có thể đóng tab vì bất mãn với thái độ câu trả lời dù thông tin đúng.
+  + Ở Phiên 2, người dùng có thể rời đi do mất mạng Internet đột ngột, có chuông cửa, hoặc có việc bận cá nhân chứ không hoàn toàn do Agent chậm.
+- **Nguyên tắc Suy luận An toàn**: Chỉ được kết luận 'Thành công' khi có **Xác nhận kép (Dual Evidence)**: Trạng thái môi trường đạt chuẩn VÀ không có cờ lỗi hệ thống. Tuyệt đối không quy kết cảm xúc chủ quan khi chỉ nhìn vào sự kiện đóng tab.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Phân loại Trạng thái Kết thúc Phiên (Session Outcome &amp; Abandonment Telemetry): Một chỉ số thô như 'Tỷ lệ rời bỏ phiên' (Session Abandonment Rate) là cực kỳ nguy hiểm nếu không gắn liền với trạng thái hoàn thành mục tiêu. Người dùng đóng chat có thể là vì họ đã có được đáp án mong muốn (Hài lòng), hoặc vì họ quá chán nản do hệ thống bị treo (Thất vọng). Việc bóc tách hai trường hợp này dựa trên trạng thái môi trường (target state verification) là mấu chốt để đánh giá đúng trải nghiệm người dùng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Workbook: User-Centric Metrics &amp; ACM Transactions on Computer-Human Interaction: Measuring Task Abandonment</t>
         </is>
       </c>
     </row>
@@ -1118,10 +1213,42 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Không để criterion khác bù hoặc làm mờ faithfulness.
-Phân tích theo nguyên lý thiết kế: Không để criterion khác bù hoặc làm mờ faithfulness.</t>
+- 1.0đ: Cô lập duy nhất một tiêu chí Faithfulness, cấm rõ ràng việc trộn lẫn style, relevance hay helpfulness.
+- 1.0đ: Định nghĩa rubric phân rã khẳng định (claim-level extraction) và tiêu chí xác định unsupported claim.
+- 1.0đ: Thiết kế lược đồ đầu ra JSON hoàn chỉnh, có các trường số liệu và phán quyết rõ ràng.
+- 1.0đ: Đảm bảo tính khả thi parse tự động trong CI/CD pipeline (zero prose outside JSON).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Viết lại Hợp đồng Giám khảo Đơn Tiêu chí (Single-criterion Judge Prompt Contract) Xuất bản JSON có thể Parse tự động:
+```text
+Bạn là một Giám khảo Đánh giá Tính Căn cứ (Faithfulness Judge) chuyên nghiệp trong hệ thống AI.
+Nhiệm vụ DUY NHẤT của bạn là đánh giá xem Câu trả lời (Answer) có được chứng minh hoàn toàn bởi Ngữ cảnh Tham chiếu (Context) hay không.
+CÁC QUY TẮC BẮT BUỘC:
+1. CHỈ đánh giá tiêu chí FAITHFULNESS (Tính trung thực dựa trên context). TUYỆT ĐỐI KHÔNG đánh giá phong cách (style), độ hữu ích (helpfulness), hay độ liên quan (relevance).
+2. Một khẳng định trong Answer được coi là 'unsupported' nếu nó chứa thông tin thực tế, số liệu hoặc tuyên bố không xuất hiện trong Context.
+3. Bắt buộc xuất kết quả theo đúng cấu trúc JSON duy nhất dưới đây, không viết thêm bất kỳ đoạn văn bản giới thiệu hay giải thích nào bên ngoài khối JSON.
+CẤU TRÚC JSON ĐẦU RA:
+{
+  "criterion": "faithfulness",
+  "verdict": "PASS" | "FAIL",
+  "faithfulness_score": &lt;float từ 0.0 đến 1.0&gt;,
+  "total_claims_count": &lt;int&gt;,
+  "unsupported_claims_count": &lt;int&gt;,
+  "unsupported_claims_list": [&lt;danh sách chuỗi các khẳng định không có căn cứ&gt;],
+  "concise_rationale": "&lt;giải thích ngắn gọn dưới 50 từ lý giải cho phán quyết&gt;"
+}
+DỮ LIỆU ĐÁNH GIÁ:
+--- CONTEXT ---
+{context}
+--- ANSWER ---
+{answer}
+```
+- **Lợi ích Kỹ thuật của Hợp đồng Mới**:
+  + **Cô lập biến số đo lường (Single Criterion)**: Loại bỏ triệt để sự nhiễu loạn khi giám khảo chấm nhầm phong cách viết hay độ dài câu chữ.
+  + **Tính khả thi trong Tự động hóa CI/CD**: Định dạng JSON nghiêm ngặt cho phép thư viện Python parse trực tiếp `json.loads(output)` và chạy các lệnh kiểm tra tự động `assert result['verdict'] == 'PASS'` mà không bị lỗi crash do prose tự do.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thiết kế Hợp đồng Nhắc cho LLM-as-a-Judge (Single-responsibility Judge Contract): Một lỗi phổ biến là yêu cầu LLM chấm đồng thời 5 tiêu chí trong một prompt văn bản tự do: kết quả trả về là một đoạn văn dài dòng, trong đó giám khảo bị thiên vị bởi văn phong mượt mà (style bias) mà bỏ qua sự thật là câu trả lời bịa đặt số liệu. Hợp đồng chuẩn mực đòi hỏi cô lập duy nhất một tiêu chí (Đơn nhiệm) và ép buộc cấu trúc JSON có schema chặt chẽ để parse tự động trong đường ống CI.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI Evals Framework Documentation &amp; Zheng et al.: Judging LLM-as-a-Judge with MT-Bench (NeurIPS 2023)</t>
         </is>
       </c>
     </row>
@@ -1200,10 +1327,30 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Số level được biện minh bằng action khác nhau.
-Phân tích theo nguyên lý thiết kế: Số level được biện minh bằng action khác nhau.</t>
+- 1.0đ: Thiết lập thang đo 3 mức rời rạc với các điểm neo định nghĩa rõ ràng gắn với 3 hành động downstream.
+- 1.0đ: Định nghĩa chuẩn xác tiêu chí chặn đứng (BLOCK_FAIL) khi thiếu điều kiện critical.
+- 1.0đ: Thiết kế cơ chế tổng hợp toán học có phân tầng rõ rệt giữa Completeness và Style.
+- 1.0đ: Áp dụng quy tắc khóa trần (Score Cap = 0) triệt tiêu điểm tổng khi vi phạm Completeness.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Thang đo Neo (Scale/Anchor), Cơ chế Tổng hợp và Giới hạn Trần (Cap) cho Tiêu chí Hoàn thiện và Phong cách:
+1. **Lựa chọn Thang đo và Điểm Neo cho Tiêu chí Hoàn thiện (Completeness Scale &amp; Actionable Anchors)**:
+- Sử dụng **Thang đo Rời rạc Ba mức (3-tier Discrete Ordinal Scale)** gắn liền trực tiếp với hành động phát hành:
+  + **Mức 2 (PASS - Chấp nhận)**: Trả lời đầy đủ 100% mọi yêu cầu nghiệp vụ và điều kiện cốt lõi.
+  + **Mức 1 (MINOR_REVISION - Yêu cầu Sửa nhẹ)**: Trả lời đúng bản chất cốt lõi nhưng thiếu một vài chi tiết định dạng thứ yếu không gây nguy hiểm.
+  + **Mức 0 (BLOCK_FAIL - Chặn đứng Tuyệt đối)**: Thiếu bất kỳ điều kiện tiên quyết mang tính sống còn (Missing Critical Condition: ví dụ thiếu cảnh báo chống chỉ định thuốc, thiếu số tiền hoàn vé).
+2. **Cơ chế Tổng hợp với Tiêu chí Phong cách (Aggregation with Style Criterion)**:
+- Giả sử Tiêu chí Phong cách (Style) được chấm trên thang điểm chuẩn hóa từ 0.0 đến 1.0 (độ trôi chảy, ngữ điệu lịch sự).
+- **Nguyên tắc Chốt chặn Phủ quyết &amp; Giới hạn Trần (Veto Gate &amp; Score Cap Rule)**:
+  $$\text{Release Score} = \begin{cases} 
+  0.0 &amp; \text{nếu } \text{Completeness} == 0 \text{ (BLOCK\_FAIL)} \\
+  \min(0.60, 0.40 + 0.20 \times \text{Style}) &amp; \text{nếu } \text{Completeness} == 1 \text{ (MINOR\_REVISION)} \\
+  0.70 + 0.30 \times \text{Style} &amp; \text{nếu } \text{Completeness} == 2 \text{ (PASS)}
+  \end{cases}$$
+- **Ý nghĩa Giới hạn Trần (Cap)**: Khi Completeness bị đánh giá là `BLOCK_FAIL` (Mức 0), điểm Release tổng thể bị **khóa cứng ở mức 0.0 (Cap = 0)**. Dù câu trả lời có văn phong mượt mà, hoa mỹ như thơ ca (Style = 1.0), câu trả lời vẫn bị đánh trượt toàn diện và bị chặn không cho release.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thiết kế Thang đo Neo Hành động được (Actionable Anchored Scales in LLM Evals): Thang điểm Likert 1-5 sao truyền thống thường vô nghĩa trong công nghiệp vì ranh giới giữa 3 sao và 4 sao rất mơ hồ. Một thang đo chuyên nghiệp phải gắn với hành động cụ thể (Accept, Minor Fix, Block). Đặc biệt, việc thiết lập quy tắc Giới hạn Trần (Score Cap) ngăn chặn cạm bẫy 'bù trừ nguy hiểm': không bao giờ cho phép sự hoa mỹ của ngôn từ (Style) bù đắp cho sự thiếu sót điều kiện kỹ thuật cốt tử (Completeness).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic: Evaluating and Improving LLM Systems &amp; Google SRE Quality Gating Guidelines</t>
         </is>
       </c>
     </row>
@@ -1286,10 +1433,25 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một item có thể cần hai decision khác nhau nhưng không copy score.
-Phân tích theo nguyên lý thiết kế: Một item có thể cần hai decision khác nhau nhưng không copy score.</t>
+- 1.0đ: Thiết kế Chế độ 1 (Absolute Compliance Gate) dùng phương pháp Reference-Based Single-Output với toàn văn hợp đồng.
+- 1.0đ: Thiết kế Chế độ 2 (A/B Preference) dùng phương pháp Blinded Pairwise Judging tập trung vào phong cách.
+- 1.0đ: Xác định đúng chính sách hiển thị tài liệu tham chiếu (Reference Visibility) riêng biệt cho từng chế độ.
+- 1.0đ: Khẳng định nguyên tắc cấm đánh tráo: chiến thắng phong cách không thay thế được sự tuân thủ pháp lý.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Cơ chế Hiển thị Tài liệu Tham chiếu (Reference Visibility) và Hai Chế độ Giám khảo Độc lập:
+1. **Chế độ Giám khảo 1: Cổng Tuân thủ Tuyệt đối (Absolute Compliance Gate)**:
+- **Mục tiêu**: Đo lường tính đúng đắn pháp lý và độ tuân thủ 100% đối với hợp đồng văn bản tin cậy (`trusted contract text`).
+- **Chế độ Thẩm định (Judging Mode)**: **Reference-Based Single-Output Judging (Thẩm định Đơn lẻ có Tham chiếu Đầy đủ)**.
+- **Chính sách Hiển thị Tài liệu Tham chiếu (Reference Visibility)**: **Full Context Visibility (Mở toàn bộ tài liệu hợp đồng cho Judge)**. Giám khảo được cung cấp trực tiếp nguyên văn văn bản hợp đồng và câu trả lời của ứng viên. Nhiệm vụ của Judge là thực thi bài kiểm tra nhị phân (Binary Pass/Fail): từng khẳng định trong câu trả lời có đúng từng câu từng chữ với điều khoản hợp đồng hay không.
+2. **Chế độ Giám khảo 2: Đánh giá Sở thích Văn phong Đối đầu A/B (A/B Preference for Style)**:
+- **Mục tiêu**: So sánh xem giữa hai câu trả lời A và B, câu nào có cách diễn đạt tự nhiên, mạch lạc, dễ hiểu và chuyên nghiệp hơn.
+- **Chế độ Thẩm định (Judging Mode)**: **Reference-Agnostic / Blinded Pairwise Judging (Thẩm định So sánh Cặp Ẩn danh)**.
+- **Chính sách Hiển thị Tài liệu Tham chiếu**: **Hidden / Restricted Context (Ẩn tài liệu hợp đồng chi tiết, chỉ cung cấp tiêu chí phong cách)**. Chế độ này chỉ chạy sau khi cả A và B đã VƯỢT QUA Chế độ 1. Khi so sánh phong cách, việc nhồi lại toàn bộ hợp đồng dài dòng sẽ gây nhiễu chú ý của Judge; chỉ cần yêu cầu Judge tập trung vào tính súc tích, ngữ điệu và cấu trúc trình bày.
+3. **Nguyên tắc Cấm Đánh tráo Khẳng định (Anti-conflation Rule)**: Một câu trả lời được người dùng 'thích hơn về văn phong' (thắng ở Chế độ 2) tuyệt đối không được suy diễn là 'đúng về mặt hợp đồng'. Tính hợp pháp phải được xác thực độc lập ở Chế độ 1.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Phân lập Chế độ Thẩm định (Decoupling Compliance Verification from Style Preference): Độ tuân thủ hợp đồng (Compliance) là thuộc tính đơn lẻ tuyệt đối (Absolute Truth) đòi hỏi phải mở toàn bộ văn bản gốc làm căn cứ. Ngược lại, sở thích văn phong (Style Preference) là thuộc tính so sánh tương đối (Relative Preference). Nếu trộn lẫn hai chế độ này vào một lượt chấm, mô hình Judge sẽ dễ dàng thiên vị câu trả lời có văn phong mượt mà nhưng vi phạm điều khoản ngầm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LMSYS Chatbot Arena: Pairwise Human &amp; LLM Evaluation &amp; Stanford HELM Evaluation Protocol</t>
         </is>
       </c>
     </row>
@@ -1404,10 +1566,23 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Aggregation không sửa được input comparison bị bias.
-Phân tích theo nguyên lý thiết kế: Aggregation không sửa được input comparison bị bias.</t>
+- 1.0đ: Vạch trần sự yếu kém của bằng chứng hiện tại do mức Position Bias 25% làm sai lệch trận A/B.
+- 1.0đ: Phân tích thấu đáo hiện tượng phi bắc cầu (Non-transitivity / Cyclic preferences) trong đánh giá LLM.
+- 1.0đ: Thiết kế bước kiểm định khử bias bằng hoán đổi vị trí (Position-swapped rematch) cho cặp A/B.
+- 1.0đ: Tổ chức trận đối đầu trực tiếp A vs C và áp dụng thuật toán Bradley-Terry tổng hợp bảng xếp hạng chuẩn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá Hiện trạng Đồ thị Xếp hạng (Ranking Graph Assessment):
+- **Dữ liệu hiện tại**: Đồ thị có hướng ghi nhận: $A$ thắng $B$ ($A \succ B$) và $B$ thắng $C$ ($B \succ C$), nhưng cặp đấu trực tiếp giữa $A$ và $C$ ($A - C$) hoàn toàn chưa được thực hiện.
+- **Lỗ hổng Thiên vị Vị trí (Severe Position Bias)**: Trận đấu $A/B$ ghi nhận tỷ lệ thiên vị vị trí lên tới **25%** (nghĩa là việc xếp A đứng trước hay đứng sau làm thay đổi kết quả tới 25%). Điều này chứng minh bằng chứng $A \succ B$ có độ tin cậy khoa học rất thấp và có thể là kết quả giả tạo do vị trí xếp đặt.
+- **Cạm bẫy Tính Bắc cầu (Non-transitivity Trap in LLMs)**: Không bao giờ được tự ý suy diễn tính chất bắc cầu '$A \succ B$ và $B \succ C \implies A \succ C$'. Nghiên cứu về LLM-as-a-Judge đã chứng minh hiện tượng 'Vòng tròn Kéo-Búa-Bao' (Cyclic Non-transitive Preference: $A \succ B, B \succ C, C \succ A$) diễn ra rất phổ biến do mỗi cặp đấu kích hoạt các thuộc tính so sánh khác nhau.
+2. Các Bước Kế tiếp Bắt buộc để Thiết lập Bảng Xếp hạng Đáng tin cậy (Next Execution Steps):
+- **Bước 1: Khử Thiên vị Vị trí cho Trận A/B (Position-swapped Debiasing for A/B)**: Chạy lại cặp đấu $A$ vs $B$ với cơ chế hoán đổi vị trí đối xứng 100%: Lượt 1 đưa `(A, B)`, Lượt 2 đưa `(B, A)`. Chỉ công nhận $A$ thắng nếu $A$ chiến thắng ở cả hai lượt hoặc thắng điểm tổng hợp sau hoán đổi.
+- **Bước 2: Tổ chức Thi đấu Trực tiếp Cặp A vs C (Direct Match A vs C with Swap)**: Chạy đối đầu trực tiếp giữa $A$ và $C$ có hoán đổi vị trí để thu thập bằng chứng thực nghiệm trực tiếp, hoàn thiện đồ thị so sánh.
+- **Bước 3: Tổng hợp Xếp hạng qua Mô hình Bradley-Terry hoặc PageRank**: Áp dụng mô hình xác suất Bradley-Terry để ước lượng điểm số tiềm ẩn (latent skill score) trên toàn bộ ma trận kết quả sau khi đã khử bias.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Xếp hạng So sánh Cặp trong AI (Pairwise Ranking &amp; Non-transitivity): Trong các hệ thống đánh giá bằng LLM như Chatbot Arena, giả định bắc cầu cổ điển thường xuyên bị phá vỡ. Một mô hình Judge có thể chọn A hơn B vì độ dài, chọn B hơn C vì số liệu, và chọn C hơn A vì phong cách. Kết hợp với thiên vị vị trí (Position Bias), một kết luận xếp hạng chỉ có giá trị khi toàn bộ các cạnh của đồ thị đều được kiểm định đối xứng qua hoán đổi vị trí (Position Swap) và mô hình hóa qua Bradley-Terry.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Lianmin Zheng et al.: Judging LLM-as-a-Judge with MT-Bench and Chatbot Arena (NeurIPS 2023) &amp; Bradley-Terry Model (1952)</t>
         </is>
       </c>
     </row>
